--- a/tests/data/masterfile_with_school_in_two_regions.xlsx
+++ b/tests/data/masterfile_with_school_in_two_regions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10409"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stef/UCL/rred-reports/tests/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/katiebuntic/projects/rred-reports/tests/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75AA5A26-CDB1-0C4E-BDC7-39087F65A1E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6566F33F-9CED-3C47-8DBB-9957CDD683C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{1F5F4F09-FFBF-FF42-8606-4D2782A9E922}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" xr2:uid="{1F5F4F09-FFBF-FF42-8606-4D2782A9E922}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="92">
   <si>
     <t>reg_rr_title</t>
   </si>
@@ -306,6 +306,15 @@
   </si>
   <si>
     <t>AAAAA</t>
+  </si>
+  <si>
+    <t>reg_deis_status</t>
+  </si>
+  <si>
+    <t>reg_lan</t>
+  </si>
+  <si>
+    <t>reg_lan_tum</t>
   </si>
 </sst>
 </file>
@@ -359,11 +368,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -678,7 +688,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01BC0FAF-0515-DD4A-8720-9B9E6959245E}">
-  <dimension ref="A1:BR41"/>
+  <dimension ref="A1:BU41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -687,10 +697,10 @@
     <col min="31" max="33" width="11" style="2"/>
     <col min="62" max="62" width="26.5" style="2" customWidth="1"/>
     <col min="66" max="66" width="38" customWidth="1"/>
-    <col min="70" max="70" width="22" customWidth="1"/>
+    <col min="73" max="73" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:70" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>82</v>
       </c>
@@ -899,10 +909,19 @@
         <v>66</v>
       </c>
       <c r="BR1" t="s">
+        <v>89</v>
+      </c>
+      <c r="BS1" t="s">
+        <v>90</v>
+      </c>
+      <c r="BT1" t="s">
+        <v>91</v>
+      </c>
+      <c r="BU1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:70" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>67</v>
       </c>
@@ -1110,8 +1129,11 @@
       <c r="BQ2" s="1" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="3" spans="1:70" x14ac:dyDescent="0.2">
+      <c r="BR2" s="4"/>
+      <c r="BS2" s="4"/>
+      <c r="BT2" s="4"/>
+    </row>
+    <row r="3" spans="1:73" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>78</v>
       </c>
@@ -1319,8 +1341,11 @@
       <c r="BQ3" s="1" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="4" spans="1:70" x14ac:dyDescent="0.2">
+      <c r="BR3" s="4"/>
+      <c r="BS3" s="4"/>
+      <c r="BT3" s="4"/>
+    </row>
+    <row r="4" spans="1:73" x14ac:dyDescent="0.2">
       <c r="G4" s="1"/>
       <c r="AF4" s="3"/>
       <c r="AO4" s="1"/>
@@ -1329,8 +1354,11 @@
       <c r="BM4" s="1"/>
       <c r="BN4" s="2"/>
       <c r="BQ4" s="1"/>
-    </row>
-    <row r="5" spans="1:70" x14ac:dyDescent="0.2">
+      <c r="BR4" s="4"/>
+      <c r="BS4" s="4"/>
+      <c r="BT4" s="4"/>
+    </row>
+    <row r="5" spans="1:73" x14ac:dyDescent="0.2">
       <c r="G5" s="1"/>
       <c r="AF5" s="3"/>
       <c r="AO5" s="1"/>
@@ -1338,8 +1366,11 @@
       <c r="BI5" s="1"/>
       <c r="BM5" s="1"/>
       <c r="BQ5" s="1"/>
-    </row>
-    <row r="6" spans="1:70" x14ac:dyDescent="0.2">
+      <c r="BR5" s="4"/>
+      <c r="BS5" s="4"/>
+      <c r="BT5" s="4"/>
+    </row>
+    <row r="6" spans="1:73" x14ac:dyDescent="0.2">
       <c r="G6" s="1"/>
       <c r="AF6" s="3"/>
       <c r="AO6" s="1"/>
@@ -1347,8 +1378,11 @@
       <c r="BI6" s="1"/>
       <c r="BM6" s="1"/>
       <c r="BQ6" s="1"/>
-    </row>
-    <row r="7" spans="1:70" x14ac:dyDescent="0.2">
+      <c r="BR6" s="4"/>
+      <c r="BS6" s="4"/>
+      <c r="BT6" s="4"/>
+    </row>
+    <row r="7" spans="1:73" x14ac:dyDescent="0.2">
       <c r="G7" s="1"/>
       <c r="AF7" s="3"/>
       <c r="AO7" s="1"/>
@@ -1356,8 +1390,11 @@
       <c r="BI7" s="1"/>
       <c r="BM7" s="1"/>
       <c r="BQ7" s="1"/>
-    </row>
-    <row r="8" spans="1:70" x14ac:dyDescent="0.2">
+      <c r="BR7" s="4"/>
+      <c r="BS7" s="4"/>
+      <c r="BT7" s="4"/>
+    </row>
+    <row r="8" spans="1:73" x14ac:dyDescent="0.2">
       <c r="G8" s="1"/>
       <c r="AF8" s="3"/>
       <c r="AO8" s="1"/>
@@ -1365,8 +1402,11 @@
       <c r="BI8" s="1"/>
       <c r="BM8" s="1"/>
       <c r="BQ8" s="1"/>
-    </row>
-    <row r="9" spans="1:70" x14ac:dyDescent="0.2">
+      <c r="BR8" s="4"/>
+      <c r="BS8" s="4"/>
+      <c r="BT8" s="4"/>
+    </row>
+    <row r="9" spans="1:73" x14ac:dyDescent="0.2">
       <c r="G9" s="1"/>
       <c r="AF9" s="3"/>
       <c r="AO9" s="1"/>
@@ -1374,8 +1414,11 @@
       <c r="BI9" s="1"/>
       <c r="BM9" s="1"/>
       <c r="BQ9" s="1"/>
-    </row>
-    <row r="10" spans="1:70" x14ac:dyDescent="0.2">
+      <c r="BR9" s="4"/>
+      <c r="BS9" s="4"/>
+      <c r="BT9" s="4"/>
+    </row>
+    <row r="10" spans="1:73" x14ac:dyDescent="0.2">
       <c r="G10" s="1"/>
       <c r="AF10" s="3"/>
       <c r="AO10" s="1"/>
@@ -1383,8 +1426,11 @@
       <c r="BI10" s="1"/>
       <c r="BM10" s="1"/>
       <c r="BQ10" s="1"/>
-    </row>
-    <row r="11" spans="1:70" x14ac:dyDescent="0.2">
+      <c r="BR10" s="4"/>
+      <c r="BS10" s="4"/>
+      <c r="BT10" s="4"/>
+    </row>
+    <row r="11" spans="1:73" x14ac:dyDescent="0.2">
       <c r="G11" s="1"/>
       <c r="AF11" s="3"/>
       <c r="AO11" s="1"/>
@@ -1392,8 +1438,11 @@
       <c r="BI11" s="1"/>
       <c r="BM11" s="1"/>
       <c r="BQ11" s="1"/>
-    </row>
-    <row r="12" spans="1:70" x14ac:dyDescent="0.2">
+      <c r="BR11" s="4"/>
+      <c r="BS11" s="4"/>
+      <c r="BT11" s="4"/>
+    </row>
+    <row r="12" spans="1:73" x14ac:dyDescent="0.2">
       <c r="G12" s="1"/>
       <c r="AF12" s="3"/>
       <c r="AO12" s="1"/>
@@ -1401,8 +1450,11 @@
       <c r="BI12" s="1"/>
       <c r="BM12" s="1"/>
       <c r="BQ12" s="1"/>
-    </row>
-    <row r="13" spans="1:70" x14ac:dyDescent="0.2">
+      <c r="BR12" s="4"/>
+      <c r="BS12" s="4"/>
+      <c r="BT12" s="4"/>
+    </row>
+    <row r="13" spans="1:73" x14ac:dyDescent="0.2">
       <c r="G13" s="1"/>
       <c r="AF13" s="3"/>
       <c r="AO13" s="1"/>
@@ -1410,8 +1462,11 @@
       <c r="BI13" s="1"/>
       <c r="BM13" s="1"/>
       <c r="BQ13" s="1"/>
-    </row>
-    <row r="14" spans="1:70" x14ac:dyDescent="0.2">
+      <c r="BR13" s="4"/>
+      <c r="BS13" s="4"/>
+      <c r="BT13" s="4"/>
+    </row>
+    <row r="14" spans="1:73" x14ac:dyDescent="0.2">
       <c r="G14" s="1"/>
       <c r="AF14" s="3"/>
       <c r="AO14" s="1"/>
@@ -1419,8 +1474,11 @@
       <c r="BI14" s="1"/>
       <c r="BM14" s="1"/>
       <c r="BQ14" s="1"/>
-    </row>
-    <row r="15" spans="1:70" x14ac:dyDescent="0.2">
+      <c r="BR14" s="4"/>
+      <c r="BS14" s="4"/>
+      <c r="BT14" s="4"/>
+    </row>
+    <row r="15" spans="1:73" x14ac:dyDescent="0.2">
       <c r="G15" s="1"/>
       <c r="AF15" s="3"/>
       <c r="AO15" s="1"/>
@@ -1428,8 +1486,11 @@
       <c r="BI15" s="1"/>
       <c r="BM15" s="1"/>
       <c r="BQ15" s="1"/>
-    </row>
-    <row r="16" spans="1:70" x14ac:dyDescent="0.2">
+      <c r="BR15" s="4"/>
+      <c r="BS15" s="4"/>
+      <c r="BT15" s="4"/>
+    </row>
+    <row r="16" spans="1:73" x14ac:dyDescent="0.2">
       <c r="G16" s="1"/>
       <c r="AF16" s="3"/>
       <c r="AO16" s="1"/>
@@ -1437,8 +1498,11 @@
       <c r="BI16" s="1"/>
       <c r="BM16" s="1"/>
       <c r="BQ16" s="1"/>
-    </row>
-    <row r="17" spans="7:69" x14ac:dyDescent="0.2">
+      <c r="BR16" s="4"/>
+      <c r="BS16" s="4"/>
+      <c r="BT16" s="4"/>
+    </row>
+    <row r="17" spans="7:72" x14ac:dyDescent="0.2">
       <c r="G17" s="1"/>
       <c r="AF17" s="3"/>
       <c r="AO17" s="1"/>
@@ -1446,8 +1510,11 @@
       <c r="BI17" s="1"/>
       <c r="BM17" s="1"/>
       <c r="BQ17" s="1"/>
-    </row>
-    <row r="18" spans="7:69" x14ac:dyDescent="0.2">
+      <c r="BR17" s="4"/>
+      <c r="BS17" s="4"/>
+      <c r="BT17" s="4"/>
+    </row>
+    <row r="18" spans="7:72" x14ac:dyDescent="0.2">
       <c r="G18" s="1"/>
       <c r="AF18" s="3"/>
       <c r="AO18" s="1"/>
@@ -1455,8 +1522,11 @@
       <c r="BI18" s="1"/>
       <c r="BM18" s="1"/>
       <c r="BQ18" s="1"/>
-    </row>
-    <row r="19" spans="7:69" x14ac:dyDescent="0.2">
+      <c r="BR18" s="4"/>
+      <c r="BS18" s="4"/>
+      <c r="BT18" s="4"/>
+    </row>
+    <row r="19" spans="7:72" x14ac:dyDescent="0.2">
       <c r="G19" s="1"/>
       <c r="AF19" s="3"/>
       <c r="AO19" s="1"/>
@@ -1464,8 +1534,11 @@
       <c r="BI19" s="1"/>
       <c r="BM19" s="1"/>
       <c r="BQ19" s="1"/>
-    </row>
-    <row r="20" spans="7:69" x14ac:dyDescent="0.2">
+      <c r="BR19" s="4"/>
+      <c r="BS19" s="4"/>
+      <c r="BT19" s="4"/>
+    </row>
+    <row r="20" spans="7:72" x14ac:dyDescent="0.2">
       <c r="G20" s="1"/>
       <c r="AF20" s="3"/>
       <c r="AO20" s="1"/>
@@ -1473,8 +1546,11 @@
       <c r="BI20" s="1"/>
       <c r="BM20" s="1"/>
       <c r="BQ20" s="1"/>
-    </row>
-    <row r="21" spans="7:69" x14ac:dyDescent="0.2">
+      <c r="BR20" s="4"/>
+      <c r="BS20" s="4"/>
+      <c r="BT20" s="4"/>
+    </row>
+    <row r="21" spans="7:72" x14ac:dyDescent="0.2">
       <c r="G21" s="1"/>
       <c r="AF21" s="3"/>
       <c r="AO21" s="1"/>
@@ -1482,8 +1558,11 @@
       <c r="BI21" s="1"/>
       <c r="BM21" s="1"/>
       <c r="BQ21" s="1"/>
-    </row>
-    <row r="22" spans="7:69" x14ac:dyDescent="0.2">
+      <c r="BR21" s="4"/>
+      <c r="BS21" s="4"/>
+      <c r="BT21" s="4"/>
+    </row>
+    <row r="22" spans="7:72" x14ac:dyDescent="0.2">
       <c r="G22" s="1"/>
       <c r="AF22" s="3"/>
       <c r="AO22" s="1"/>
@@ -1491,8 +1570,11 @@
       <c r="BI22" s="1"/>
       <c r="BM22" s="1"/>
       <c r="BQ22" s="1"/>
-    </row>
-    <row r="23" spans="7:69" x14ac:dyDescent="0.2">
+      <c r="BR22" s="4"/>
+      <c r="BS22" s="4"/>
+      <c r="BT22" s="4"/>
+    </row>
+    <row r="23" spans="7:72" x14ac:dyDescent="0.2">
       <c r="G23" s="1"/>
       <c r="AF23" s="3"/>
       <c r="AO23" s="1"/>
@@ -1500,8 +1582,11 @@
       <c r="BI23" s="1"/>
       <c r="BM23" s="1"/>
       <c r="BQ23" s="1"/>
-    </row>
-    <row r="24" spans="7:69" x14ac:dyDescent="0.2">
+      <c r="BR23" s="4"/>
+      <c r="BS23" s="4"/>
+      <c r="BT23" s="4"/>
+    </row>
+    <row r="24" spans="7:72" x14ac:dyDescent="0.2">
       <c r="G24" s="1"/>
       <c r="AF24" s="3"/>
       <c r="AO24" s="1"/>
@@ -1509,8 +1594,11 @@
       <c r="BI24" s="1"/>
       <c r="BM24" s="1"/>
       <c r="BQ24" s="1"/>
-    </row>
-    <row r="25" spans="7:69" x14ac:dyDescent="0.2">
+      <c r="BR24" s="4"/>
+      <c r="BS24" s="4"/>
+      <c r="BT24" s="4"/>
+    </row>
+    <row r="25" spans="7:72" x14ac:dyDescent="0.2">
       <c r="G25" s="1"/>
       <c r="AF25" s="3"/>
       <c r="AO25" s="1"/>
@@ -1518,8 +1606,11 @@
       <c r="BI25" s="1"/>
       <c r="BM25" s="1"/>
       <c r="BQ25" s="1"/>
-    </row>
-    <row r="26" spans="7:69" x14ac:dyDescent="0.2">
+      <c r="BR25" s="4"/>
+      <c r="BS25" s="4"/>
+      <c r="BT25" s="4"/>
+    </row>
+    <row r="26" spans="7:72" x14ac:dyDescent="0.2">
       <c r="G26" s="1"/>
       <c r="AF26" s="3"/>
       <c r="AO26" s="1"/>
@@ -1527,8 +1618,11 @@
       <c r="BI26" s="1"/>
       <c r="BM26" s="1"/>
       <c r="BQ26" s="1"/>
-    </row>
-    <row r="27" spans="7:69" x14ac:dyDescent="0.2">
+      <c r="BR26" s="4"/>
+      <c r="BS26" s="4"/>
+      <c r="BT26" s="4"/>
+    </row>
+    <row r="27" spans="7:72" x14ac:dyDescent="0.2">
       <c r="G27" s="1"/>
       <c r="AF27" s="3"/>
       <c r="AO27" s="1"/>
@@ -1536,8 +1630,11 @@
       <c r="BI27" s="1"/>
       <c r="BM27" s="1"/>
       <c r="BQ27" s="1"/>
-    </row>
-    <row r="28" spans="7:69" x14ac:dyDescent="0.2">
+      <c r="BR27" s="4"/>
+      <c r="BS27" s="4"/>
+      <c r="BT27" s="4"/>
+    </row>
+    <row r="28" spans="7:72" x14ac:dyDescent="0.2">
       <c r="G28" s="1"/>
       <c r="AF28" s="3"/>
       <c r="AO28" s="1"/>
@@ -1545,8 +1642,11 @@
       <c r="BI28" s="1"/>
       <c r="BM28" s="1"/>
       <c r="BQ28" s="1"/>
-    </row>
-    <row r="29" spans="7:69" x14ac:dyDescent="0.2">
+      <c r="BR28" s="4"/>
+      <c r="BS28" s="4"/>
+      <c r="BT28" s="4"/>
+    </row>
+    <row r="29" spans="7:72" x14ac:dyDescent="0.2">
       <c r="G29" s="1"/>
       <c r="AF29" s="3"/>
       <c r="AO29" s="1"/>
@@ -1554,8 +1654,11 @@
       <c r="BI29" s="1"/>
       <c r="BM29" s="1"/>
       <c r="BQ29" s="1"/>
-    </row>
-    <row r="30" spans="7:69" x14ac:dyDescent="0.2">
+      <c r="BR29" s="4"/>
+      <c r="BS29" s="4"/>
+      <c r="BT29" s="4"/>
+    </row>
+    <row r="30" spans="7:72" x14ac:dyDescent="0.2">
       <c r="G30" s="1"/>
       <c r="AF30" s="3"/>
       <c r="AO30" s="1"/>
@@ -1563,8 +1666,11 @@
       <c r="BI30" s="1"/>
       <c r="BM30" s="1"/>
       <c r="BQ30" s="1"/>
-    </row>
-    <row r="31" spans="7:69" x14ac:dyDescent="0.2">
+      <c r="BR30" s="4"/>
+      <c r="BS30" s="4"/>
+      <c r="BT30" s="4"/>
+    </row>
+    <row r="31" spans="7:72" x14ac:dyDescent="0.2">
       <c r="G31" s="1"/>
       <c r="AF31" s="3"/>
       <c r="AO31" s="1"/>
@@ -1572,8 +1678,11 @@
       <c r="BI31" s="1"/>
       <c r="BM31" s="1"/>
       <c r="BQ31" s="1"/>
-    </row>
-    <row r="32" spans="7:69" x14ac:dyDescent="0.2">
+      <c r="BR31" s="4"/>
+      <c r="BS31" s="4"/>
+      <c r="BT31" s="4"/>
+    </row>
+    <row r="32" spans="7:72" x14ac:dyDescent="0.2">
       <c r="G32" s="1"/>
       <c r="AF32" s="3"/>
       <c r="AO32" s="1"/>
@@ -1581,8 +1690,11 @@
       <c r="BI32" s="1"/>
       <c r="BM32" s="1"/>
       <c r="BQ32" s="1"/>
-    </row>
-    <row r="33" spans="7:69" x14ac:dyDescent="0.2">
+      <c r="BR32" s="4"/>
+      <c r="BS32" s="4"/>
+      <c r="BT32" s="4"/>
+    </row>
+    <row r="33" spans="7:72" x14ac:dyDescent="0.2">
       <c r="G33" s="1"/>
       <c r="AF33" s="3"/>
       <c r="AO33" s="1"/>
@@ -1590,8 +1702,11 @@
       <c r="BI33" s="1"/>
       <c r="BM33" s="1"/>
       <c r="BQ33" s="1"/>
-    </row>
-    <row r="34" spans="7:69" x14ac:dyDescent="0.2">
+      <c r="BR33" s="4"/>
+      <c r="BS33" s="4"/>
+      <c r="BT33" s="4"/>
+    </row>
+    <row r="34" spans="7:72" x14ac:dyDescent="0.2">
       <c r="G34" s="1"/>
       <c r="AF34" s="3"/>
       <c r="AO34" s="1"/>
@@ -1599,8 +1714,11 @@
       <c r="BI34" s="1"/>
       <c r="BM34" s="1"/>
       <c r="BQ34" s="1"/>
-    </row>
-    <row r="35" spans="7:69" x14ac:dyDescent="0.2">
+      <c r="BR34" s="4"/>
+      <c r="BS34" s="4"/>
+      <c r="BT34" s="4"/>
+    </row>
+    <row r="35" spans="7:72" x14ac:dyDescent="0.2">
       <c r="G35" s="1"/>
       <c r="AF35" s="3"/>
       <c r="AO35" s="1"/>
@@ -1608,8 +1726,11 @@
       <c r="BI35" s="1"/>
       <c r="BM35" s="1"/>
       <c r="BQ35" s="1"/>
-    </row>
-    <row r="36" spans="7:69" x14ac:dyDescent="0.2">
+      <c r="BR35" s="4"/>
+      <c r="BS35" s="4"/>
+      <c r="BT35" s="4"/>
+    </row>
+    <row r="36" spans="7:72" x14ac:dyDescent="0.2">
       <c r="G36" s="1"/>
       <c r="AF36" s="3"/>
       <c r="AO36" s="1"/>
@@ -1617,8 +1738,11 @@
       <c r="BI36" s="1"/>
       <c r="BM36" s="1"/>
       <c r="BQ36" s="1"/>
-    </row>
-    <row r="37" spans="7:69" x14ac:dyDescent="0.2">
+      <c r="BR36" s="4"/>
+      <c r="BS36" s="4"/>
+      <c r="BT36" s="4"/>
+    </row>
+    <row r="37" spans="7:72" x14ac:dyDescent="0.2">
       <c r="G37" s="1"/>
       <c r="AF37" s="3"/>
       <c r="AO37" s="1"/>
@@ -1626,8 +1750,11 @@
       <c r="BI37" s="1"/>
       <c r="BM37" s="1"/>
       <c r="BQ37" s="1"/>
-    </row>
-    <row r="38" spans="7:69" x14ac:dyDescent="0.2">
+      <c r="BR37" s="4"/>
+      <c r="BS37" s="4"/>
+      <c r="BT37" s="4"/>
+    </row>
+    <row r="38" spans="7:72" x14ac:dyDescent="0.2">
       <c r="G38" s="1"/>
       <c r="AF38" s="3"/>
       <c r="AO38" s="1"/>
@@ -1635,8 +1762,11 @@
       <c r="BI38" s="1"/>
       <c r="BM38" s="1"/>
       <c r="BQ38" s="1"/>
-    </row>
-    <row r="39" spans="7:69" x14ac:dyDescent="0.2">
+      <c r="BR38" s="4"/>
+      <c r="BS38" s="4"/>
+      <c r="BT38" s="4"/>
+    </row>
+    <row r="39" spans="7:72" x14ac:dyDescent="0.2">
       <c r="G39" s="1"/>
       <c r="AF39" s="3"/>
       <c r="AO39" s="1"/>
@@ -1644,8 +1774,11 @@
       <c r="BI39" s="1"/>
       <c r="BM39" s="1"/>
       <c r="BQ39" s="1"/>
-    </row>
-    <row r="40" spans="7:69" x14ac:dyDescent="0.2">
+      <c r="BR39" s="4"/>
+      <c r="BS39" s="4"/>
+      <c r="BT39" s="4"/>
+    </row>
+    <row r="40" spans="7:72" x14ac:dyDescent="0.2">
       <c r="G40" s="1"/>
       <c r="AF40" s="3"/>
       <c r="AO40" s="1"/>
@@ -1653,8 +1786,11 @@
       <c r="BI40" s="1"/>
       <c r="BM40" s="1"/>
       <c r="BQ40" s="1"/>
-    </row>
-    <row r="41" spans="7:69" x14ac:dyDescent="0.2">
+      <c r="BR40" s="4"/>
+      <c r="BS40" s="4"/>
+      <c r="BT40" s="4"/>
+    </row>
+    <row r="41" spans="7:72" x14ac:dyDescent="0.2">
       <c r="G41" s="1"/>
       <c r="AF41" s="3"/>
       <c r="AO41" s="1"/>
@@ -1662,6 +1798,9 @@
       <c r="BI41" s="1"/>
       <c r="BM41" s="1"/>
       <c r="BQ41" s="1"/>
+      <c r="BR41" s="4"/>
+      <c r="BS41" s="4"/>
+      <c r="BT41" s="4"/>
     </row>
   </sheetData>
   <autoFilter ref="F1:F36" xr:uid="{01BC0FAF-0515-DD4A-8720-9B9E6959245E}"/>
